--- a/data/trans_orig/IP07_C16_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C16_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han sufrido cyberbulling en 2023 (tasa de respuesta: 99,48%)</t>
+          <t>Menores según si han sufrido cyberbulling en su colegio/instituto o fuera de él en 2023 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16189</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13559</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>80,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12016</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13610</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16158</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>13329</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16754</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>79,55%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>37</t>
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>29799</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26163</t>
+          <t>26935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3438</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>20,45%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2608</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12016</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12016</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12016</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>187780</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>172292</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>193816</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>123985</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>69484</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>151078</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>78,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>43,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>188972</t>
+          <t>131267</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>169154</t>
+          <t>121917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>195846</t>
+          <t>136213</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>312956</t>
+          <t>319047</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>236888</t>
+          <t>302257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>341319</t>
+          <t>328149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22157</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>29372</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>87839</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>55,38%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26737</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>113921</t>
+          <t>27604</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6417</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3084</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11735</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5246</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10287</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>199456</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>199456</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>199456</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>158603</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>158603</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>158603</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>201879</t>
+          <t>141862</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>201879</t>
+          <t>141862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201879</t>
+          <t>141862</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>360482</t>
+          <t>341318</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>360482</t>
+          <t>341318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360482</t>
+          <t>341318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,107 +1632,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51127</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46339</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>87,43%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>36717</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33383</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38102</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>86,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>38784</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>34776</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>40321</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>94,67%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>84,88%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>89911</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>85176</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>92397</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>90,64%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>98,32%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>50824</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>45429</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>52693</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>87540</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>82963</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>89874</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>95,73%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -1858,107 +1858,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1877</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6665</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5369</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2185</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6193</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>4063</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>8798</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1869</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7264</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3905</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1571</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>8482</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>255095</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>240135</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>261993</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>89,2%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>172717</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>111625</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>199742</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>255953</t>
+          <t>183661</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234539</t>
+          <t>172982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>262989</t>
+          <t>189085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>428671</t>
+          <t>438757</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340510</t>
+          <t>421382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459204</t>
+          <t>448408</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24872</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>29372</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>91786</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128736</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15630</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>7281</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13710</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>269223</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>209371</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>271326</t>
+          <t>196441</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480698</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
